--- a/data/trans_dic/P04D$colectiva-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,11</t>
+          <t>2,48; 6,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,19</t>
+          <t>2,31; 6,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 15,56</t>
+          <t>5,2; 15,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,17</t>
+          <t>1,85; 5,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,89</t>
+          <t>0,96; 3,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,3</t>
+          <t>4,78; 12,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,03</t>
+          <t>2,45; 5,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,68</t>
+          <t>2,06; 4,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,01</t>
+          <t>5,86; 12,37</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,98</t>
+          <t>2,86; 5,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,7</t>
+          <t>1,92; 4,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,5</t>
+          <t>2,74; 7,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,85</t>
+          <t>2,1; 4,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,29</t>
+          <t>1,66; 4,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,27</t>
+          <t>3,8; 9,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,94</t>
+          <t>2,78; 4,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,17</t>
+          <t>2,14; 4,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,56</t>
+          <t>3,82; 7,48</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,2</t>
+          <t>1,75; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,3</t>
+          <t>1,81; 4,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,31</t>
+          <t>5,04; 9,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,59</t>
+          <t>1,94; 4,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,7</t>
+          <t>1,35; 3,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,91</t>
+          <t>4,89; 9,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,83</t>
+          <t>2,07; 3,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,61</t>
+          <t>1,84; 3,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,46</t>
+          <t>5,57; 8,44</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,36</t>
+          <t>2,22; 5,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,73</t>
+          <t>1,72; 4,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,96</t>
+          <t>1,91; 6,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,06</t>
+          <t>1,85; 5,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,22</t>
+          <t>2,17; 5,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,22</t>
+          <t>5,28; 8,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,69</t>
+          <t>2,49; 4,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,34</t>
+          <t>2,23; 4,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,83</t>
+          <t>3,28; 7,02</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,93</t>
+          <t>1,07; 3,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,33</t>
+          <t>1,16; 4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,87</t>
+          <t>3,47; 6,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,72</t>
+          <t>1,39; 4,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,67</t>
+          <t>1,1; 3,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,69</t>
+          <t>4,62; 7,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,71</t>
+          <t>1,55; 3,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,35</t>
+          <t>1,38; 3,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,69</t>
+          <t>4,52; 6,77</t>
         </is>
       </c>
     </row>
@@ -1233,42 +1233,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,21</t>
+          <t>0,54; 3,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,18</t>
+          <t>5,7; 10,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,21</t>
+          <t>0,55; 3,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,81</t>
+          <t>1,35; 4,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,27</t>
+          <t>1,37; 6,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,52</t>
+          <t>0,62; 2,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,36</t>
+          <t>1,26; 3,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,17</t>
+          <t>2,35; 7,06</t>
         </is>
       </c>
     </row>
@@ -1338,37 +1338,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,43</t>
+          <t>0,9; 6,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,15</t>
+          <t>0,79; 4,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,25</t>
+          <t>3,89; 7,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,46</t>
+          <t>0,27; 2,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,72</t>
+          <t>0,32; 3,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,97</t>
+          <t>1,84; 4,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,12</t>
+          <t>0,85; 3,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,28</t>
+          <t>2,99; 5,12</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,78</t>
+          <t>2,57; 3,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,41</t>
+          <t>2,26; 3,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,9</t>
+          <t>4,52; 6,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,33</t>
+          <t>2,16; 3,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,02</t>
+          <t>1,98; 3,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,68</t>
+          <t>4,74; 6,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,33</t>
+          <t>2,54; 3,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,04</t>
+          <t>2,26; 3,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,51</t>
+          <t>4,99; 6,51</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10669; 27620</t>
+          <t>11230; 28751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10077; 25973</t>
+          <t>9698; 26104</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22075; 62218</t>
+          <t>20784; 62862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7858; 22133</t>
+          <t>7914; 22552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3822; 15399</t>
+          <t>3810; 15535</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15132; 38520</t>
+          <t>14979; 38777</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22168; 44256</t>
+          <t>21560; 45297</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16388; 38119</t>
+          <t>16822; 36389</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42002; 85652</t>
+          <t>41764; 88231</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19960; 41108</t>
+          <t>19618; 40046</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11022; 27752</t>
+          <t>11356; 28298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10895; 31774</t>
+          <t>11592; 33147</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11883; 29582</t>
+          <t>12791; 29519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9532; 24202</t>
+          <t>9360; 23687</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19181; 47348</t>
+          <t>19387; 46547</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34683; 64110</t>
+          <t>36039; 64146</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23976; 48172</t>
+          <t>24689; 46331</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36113; 70613</t>
+          <t>35645; 69835</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12031; 28581</t>
+          <t>11919; 28352</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11540; 28804</t>
+          <t>12103; 29090</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25948; 49642</t>
+          <t>26884; 50257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13571; 32585</t>
+          <t>13754; 33244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9067; 24462</t>
+          <t>8910; 24923</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29501; 52668</t>
+          <t>28918; 53263</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29008; 53210</t>
+          <t>28774; 54426</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25176; 48040</t>
+          <t>24469; 48408</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61926; 95050</t>
+          <t>62579; 94908</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14547; 32735</t>
+          <t>13584; 32246</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11483; 30566</t>
+          <t>11105; 31276</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16670; 61818</t>
+          <t>16942; 60528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11462; 31106</t>
+          <t>11354; 30995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14492; 33882</t>
+          <t>14107; 33747</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35921; 58408</t>
+          <t>37508; 58665</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30237; 57490</t>
+          <t>30549; 54912</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30139; 56151</t>
+          <t>28901; 56867</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52757; 109259</t>
+          <t>52512; 112210</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4182; 16859</t>
+          <t>4616; 17079</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5564; 20685</t>
+          <t>5522; 20570</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19095; 38439</t>
+          <t>19412; 37433</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6013; 21153</t>
+          <t>6227; 20660</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4658; 18239</t>
+          <t>5462; 19336</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26491; 41990</t>
+          <t>25224; 41622</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13014; 32510</t>
+          <t>13619; 33040</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13422; 32677</t>
+          <t>13427; 34341</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49244; 73940</t>
+          <t>49928; 74778</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1006; 9948</t>
+          <t>989; 9957</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1788; 10744</t>
+          <t>1791; 10847</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20818; 37418</t>
+          <t>20945; 37402</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1911; 11376</t>
+          <t>1938; 10945</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5051; 18165</t>
+          <t>5105; 18373</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8189; 38063</t>
+          <t>8310; 39128</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4262; 16742</t>
+          <t>4105; 17320</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9002; 23920</t>
+          <t>8966; 23466</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24616; 69921</t>
+          <t>22862; 68799</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2255; 16013</t>
+          <t>2233; 15685</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1611; 10677</t>
+          <t>2024; 10545</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11431; 23324</t>
+          <t>10998; 22275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1007; 9555</t>
+          <t>1068; 10593</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1257; 14872</t>
+          <t>1297; 15359</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7749; 16897</t>
+          <t>7825; 17315</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5380; 19895</t>
+          <t>5410; 21253</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5147; 20863</t>
+          <t>5100; 20814</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21656; 37365</t>
+          <t>21163; 36223</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87160; 129163</t>
+          <t>87767; 130727</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>76959; 115788</t>
+          <t>76700; 116207</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>157265; 238211</t>
+          <t>156025; 240011</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>76214; 118292</t>
+          <t>76675; 117981</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>70912; 107083</t>
+          <t>70305; 107476</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>176683; 247518</t>
+          <t>175549; 242422</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>174013; 232053</t>
+          <t>177222; 234637</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>157173; 211025</t>
+          <t>156731; 211574</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>359613; 465817</t>
+          <t>357292; 466268</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$colectiva-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,36</t>
+          <t>2,2; 6,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,22</t>
+          <t>2,31; 6,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 15,72</t>
+          <t>4,36; 11,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,27</t>
+          <t>1,76; 5,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,93</t>
+          <t>0,76; 3,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 12,38</t>
+          <t>4,64; 11,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,14</t>
+          <t>2,6; 5,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,46</t>
+          <t>1,93; 4,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,37</t>
+          <t>5,2; 10,14</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,83</t>
+          <t>2,82; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,79</t>
+          <t>1,83; 4,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,83</t>
+          <t>2,78; 7,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,84</t>
+          <t>2,06; 5,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,2</t>
+          <t>1,59; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,12</t>
+          <t>4,68; 9,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,94</t>
+          <t>2,84; 4,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,01</t>
+          <t>2,05; 4,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,48</t>
+          <t>4,23; 7,34</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,16</t>
+          <t>1,74; 4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,35</t>
+          <t>1,7; 4,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 9,43</t>
+          <t>4,33; 8,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,68</t>
+          <t>1,94; 4,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,77</t>
+          <t>1,39; 3,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,01</t>
+          <t>5,3; 8,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,91</t>
+          <t>2,05; 3,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,64</t>
+          <t>1,89; 3,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,44</t>
+          <t>5,35; 7,86</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,28</t>
+          <t>2,31; 5,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,84</t>
+          <t>1,81; 4,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,82</t>
+          <t>4,44; 8,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,04</t>
+          <t>1,9; 4,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,2</t>
+          <t>2,2; 5,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,25</t>
+          <t>5,6; 8,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,48</t>
+          <t>2,48; 4,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,39</t>
+          <t>2,39; 4,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,02</t>
+          <t>5,38; 7,71</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,98</t>
+          <t>1,0; 4,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,3</t>
+          <t>1,11; 4,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,69</t>
+          <t>3,58; 6,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,61</t>
+          <t>1,36; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,89</t>
+          <t>0,96; 3,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,62</t>
+          <t>4,84; 7,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,77</t>
+          <t>1,56; 3,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,52</t>
+          <t>1,45; 3,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,77</t>
+          <t>4,31; 6,58</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,21</t>
+          <t>0,32; 3,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,24</t>
+          <t>0,53; 3,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,18</t>
+          <t>5,39; 9,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,09</t>
+          <t>0,55; 3,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,86</t>
+          <t>1,37; 5,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,44</t>
+          <t>4,27; 7,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,61</t>
+          <t>0,63; 2,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,3</t>
+          <t>1,26; 3,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,06</t>
+          <t>5,14; 7,65</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,3</t>
+          <t>0,9; 5,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,1</t>
+          <t>0,63; 4,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,88</t>
+          <t>3,66; 7,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,72</t>
+          <t>0,26; 2,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,84</t>
+          <t>0,32; 3,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,07</t>
+          <t>1,82; 4,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,33</t>
+          <t>0,85; 3,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,17</t>
+          <t>0,81; 3,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,12</t>
+          <t>2,89; 4,94</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,82</t>
+          <t>2,52; 3,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,42</t>
+          <t>2,3; 3,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,95</t>
+          <t>5,14; 6,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,32</t>
+          <t>2,13; 3,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,03</t>
+          <t>2,01; 3,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,54</t>
+          <t>5,44; 6,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,36</t>
+          <t>2,54; 3,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,05</t>
+          <t>2,27; 3,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,99; 6,51</t>
+          <t>5,46; 6,56</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>56772</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11230; 28751</t>
+          <t>9963; 27533</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9698; 26104</t>
+          <t>9695; 26825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20784; 62862</t>
+          <t>17619; 46956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7914; 22552</t>
+          <t>7550; 22295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3810; 15535</t>
+          <t>3018; 14466</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14979; 38777</t>
+          <t>16826; 41265</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21560; 45297</t>
+          <t>22930; 45748</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16822; 36389</t>
+          <t>15699; 35931</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41764; 88231</t>
+          <t>39905; 77812</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33084</t>
+          <t>33330</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>55620</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19618; 40046</t>
+          <t>19359; 40878</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11356; 28298</t>
+          <t>10835; 28310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11592; 33147</t>
+          <t>13242; 35639</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12791; 29519</t>
+          <t>12588; 30557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9360; 23687</t>
+          <t>8964; 23458</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19387; 46547</t>
+          <t>23381; 46591</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36039; 64146</t>
+          <t>36900; 62983</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24689; 46331</t>
+          <t>23668; 46407</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35645; 69835</t>
+          <t>41353; 71672</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>37363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>43094</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77725</t>
+          <t>80457</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11919; 28352</t>
+          <t>11831; 30039</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12103; 29090</t>
+          <t>11407; 29103</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26884; 50257</t>
+          <t>26657; 51411</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13754; 33244</t>
+          <t>13794; 33294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8910; 24923</t>
+          <t>9204; 24213</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28918; 53263</t>
+          <t>32962; 55500</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28774; 54426</t>
+          <t>28467; 53567</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24469; 48408</t>
+          <t>25159; 47251</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62579; 94908</t>
+          <t>66178; 97289</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39839</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47354</t>
+          <t>50145</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>87192</t>
+          <t>92673</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13584; 32246</t>
+          <t>14148; 32169</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11105; 31276</t>
+          <t>11687; 30226</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16942; 60528</t>
+          <t>31114; 56638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11354; 30995</t>
+          <t>11703; 30284</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14107; 33747</t>
+          <t>14295; 34806</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37508; 58665</t>
+          <t>41163; 62136</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30549; 54912</t>
+          <t>30396; 55896</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28901; 56867</t>
+          <t>30974; 56857</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52512; 112210</t>
+          <t>77257; 110618</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>66599</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4616; 17079</t>
+          <t>4279; 17201</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5522; 20570</t>
+          <t>5302; 21589</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19412; 37433</t>
+          <t>21759; 40112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6227; 20660</t>
+          <t>6089; 21423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5462; 19336</t>
+          <t>4755; 18418</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25224; 41622</t>
+          <t>29355; 47126</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13619; 33040</t>
+          <t>13708; 32914</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13427; 34341</t>
+          <t>14182; 33899</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49928; 74778</t>
+          <t>52305; 79892</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>53473</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>989; 9957</t>
+          <t>1001; 10034</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1791; 10847</t>
+          <t>1777; 10711</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20945; 37402</t>
+          <t>21910; 38563</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1938; 10945</t>
+          <t>1951; 11046</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5105; 18373</t>
+          <t>5161; 19417</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8310; 39128</t>
+          <t>18697; 32210</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4105; 17320</t>
+          <t>4180; 17449</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8966; 23466</t>
+          <t>8972; 23764</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22862; 68799</t>
+          <t>43374; 64602</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>29774</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2233; 15685</t>
+          <t>2243; 14879</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2024; 10545</t>
+          <t>1617; 10480</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10998; 22275</t>
+          <t>11357; 24132</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1068; 10593</t>
+          <t>1013; 9593</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1297; 15359</t>
+          <t>1284; 14121</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7825; 17315</t>
+          <t>8451; 18872</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5410; 21253</t>
+          <t>5407; 21274</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5100; 20814</t>
+          <t>5304; 22227</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21163; 36223</t>
+          <t>22373; 38245</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>203541</t>
+          <t>207080</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>418488</t>
+          <t>435368</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87767; 130727</t>
+          <t>86186; 129469</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>76700; 116207</t>
+          <t>77926; 115937</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>156025; 240011</t>
+          <t>181171; 236711</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>76675; 117981</t>
+          <t>75749; 116826</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>70305; 107476</t>
+          <t>71198; 108427</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>175549; 242422</t>
+          <t>202710; 254958</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>177222; 234637</t>
+          <t>177480; 238128</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>156731; 211574</t>
+          <t>157320; 213105</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>357292; 466268</t>
+          <t>396060; 475223</t>
         </is>
       </c>
     </row>
